--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{742C5587-AE8C-4222-A7FC-104DE6CD6860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD69560F-9D1A-4D0C-8E0D-03DBE72B4D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{FA3E43D3-216A-41E5-B6D3-E11E0DBDEE08}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7DCE6202-A540-4832-9A21-B34225140D9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="101">
   <si>
     <t>종목코드</t>
   </si>
@@ -84,28 +84,28 @@
     <t>LX인터내셔널</t>
   </si>
   <si>
-    <t>001270</t>
-  </si>
-  <si>
-    <t>부국증권</t>
-  </si>
-  <si>
     <t>001430</t>
   </si>
   <si>
     <t>세아베스틸지주</t>
   </si>
   <si>
-    <t>002310</t>
-  </si>
-  <si>
-    <t>아세아제지</t>
-  </si>
-  <si>
-    <t>003300</t>
-  </si>
-  <si>
-    <t>한일홀딩스</t>
+    <t>001740</t>
+  </si>
+  <si>
+    <t>SK네트웍스</t>
+  </si>
+  <si>
+    <t>001800</t>
+  </si>
+  <si>
+    <t>오리온홀딩스</t>
+  </si>
+  <si>
+    <t>002960</t>
+  </si>
+  <si>
+    <t>한국쉘석유</t>
   </si>
   <si>
     <t>003540</t>
@@ -126,10 +126,10 @@
     <t>코리안리</t>
   </si>
   <si>
-    <t>004980</t>
-  </si>
-  <si>
-    <t>성신양회</t>
+    <t>005180</t>
+  </si>
+  <si>
+    <t>빙그레</t>
   </si>
   <si>
     <t>005380</t>
@@ -144,28 +144,22 @@
     <t>DB손해보험</t>
   </si>
   <si>
+    <t>005850</t>
+  </si>
+  <si>
+    <t>에스엘</t>
+  </si>
+  <si>
     <t>005940</t>
   </si>
   <si>
     <t>NH투자증권</t>
   </si>
   <si>
-    <t>007340</t>
-  </si>
-  <si>
-    <t>DN오토모티브</t>
-  </si>
-  <si>
-    <t>009970</t>
-  </si>
-  <si>
-    <t>영원무역홀딩스</t>
-  </si>
-  <si>
-    <t>011780</t>
-  </si>
-  <si>
-    <t>금호석유화학</t>
+    <t>009540</t>
+  </si>
+  <si>
+    <t>HD한국조선해양</t>
   </si>
   <si>
     <t>016360</t>
@@ -174,6 +168,12 @@
     <t>삼성증권</t>
   </si>
   <si>
+    <t>016380</t>
+  </si>
+  <si>
+    <t>KG스틸</t>
+  </si>
+  <si>
     <t>017670</t>
   </si>
   <si>
@@ -216,12 +216,6 @@
     <t>LG유플러스</t>
   </si>
   <si>
-    <t>032830</t>
-  </si>
-  <si>
-    <t>삼성생명</t>
-  </si>
-  <si>
     <t>033780</t>
   </si>
   <si>
@@ -240,12 +234,36 @@
     <t>한국가스공사</t>
   </si>
   <si>
+    <t>039490</t>
+  </si>
+  <si>
+    <t>키움증권</t>
+  </si>
+  <si>
+    <t>047050</t>
+  </si>
+  <si>
+    <t>포스코인터내셔널</t>
+  </si>
+  <si>
+    <t>052400</t>
+  </si>
+  <si>
+    <t>코나아이</t>
+  </si>
+  <si>
     <t>055550</t>
   </si>
   <si>
     <t>신한지주</t>
   </si>
   <si>
+    <t>069260</t>
+  </si>
+  <si>
+    <t>TKG휴켐스</t>
+  </si>
+  <si>
     <t>071050</t>
   </si>
   <si>
@@ -282,40 +300,34 @@
     <t>iM금융지주</t>
   </si>
   <si>
-    <t>161390</t>
-  </si>
-  <si>
-    <t>한국타이어앤테크놀로</t>
-  </si>
-  <si>
     <t>175330</t>
   </si>
   <si>
     <t>JB금융지주</t>
   </si>
   <si>
-    <t>183190</t>
-  </si>
-  <si>
-    <t>아세아시멘트</t>
-  </si>
-  <si>
-    <t>192080</t>
-  </si>
-  <si>
-    <t>더블유게임즈</t>
-  </si>
-  <si>
     <t>214320</t>
   </si>
   <si>
     <t>이노션</t>
   </si>
   <si>
+    <t>241560</t>
+  </si>
+  <si>
+    <t>두산밥캣</t>
+  </si>
+  <si>
     <t>316140</t>
   </si>
   <si>
     <t>우리금융지주</t>
+  </si>
+  <si>
+    <t>383800</t>
+  </si>
+  <si>
+    <t>LX홀딩스</t>
   </si>
 </sst>
 </file>
@@ -693,21 +705,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CF557A4-D915-415E-837C-52060C745A6F}">
-  <dimension ref="A1:M44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B55D34-54E5-4ED8-828A-0F25C2BD0D6C}">
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="6.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.8984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="6.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.3984375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.3984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -759,37 +771,37 @@
         <v>12</v>
       </c>
       <c r="C2" s="2">
-        <v>25100</v>
+        <v>24750</v>
       </c>
       <c r="D2" s="3">
-        <v>3.2899999999999999E-2</v>
+        <v>4.1000000000000003E-3</v>
       </c>
       <c r="E2">
         <v>7.52</v>
       </c>
       <c r="F2">
-        <v>7.52</v>
+        <v>8.27</v>
       </c>
       <c r="G2">
         <v>6.85</v>
       </c>
       <c r="H2" s="4">
-        <v>50396.34</v>
+        <v>54762.47</v>
       </c>
       <c r="I2">
-        <v>4.38</v>
+        <v>4.4400000000000004</v>
       </c>
       <c r="J2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K2">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L2">
-        <v>101.81</v>
+        <v>101.28</v>
       </c>
       <c r="M2">
-        <v>4.58</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -800,37 +812,37 @@
         <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>157600</v>
+        <v>121600</v>
       </c>
       <c r="D3" s="3">
-        <v>1.9400000000000001E-2</v>
+        <v>5.7999999999999996E-3</v>
       </c>
       <c r="E3">
         <v>12.92</v>
       </c>
       <c r="F3">
-        <v>12.92</v>
+        <v>11.61</v>
       </c>
       <c r="G3">
         <v>17.48</v>
       </c>
       <c r="H3" s="4">
-        <v>157169.68</v>
+        <v>166439.12</v>
       </c>
       <c r="I3">
-        <v>4.3099999999999996</v>
+        <v>5.59</v>
       </c>
       <c r="J3">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="K3">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="L3">
-        <v>102.21</v>
+        <v>94.7</v>
       </c>
       <c r="M3">
-        <v>-1.01</v>
+        <v>-7.53</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
@@ -841,37 +853,37 @@
         <v>16</v>
       </c>
       <c r="C4" s="2">
-        <v>490000</v>
+        <v>655000</v>
       </c>
       <c r="D4" s="3">
-        <v>1.9800000000000002E-2</v>
+        <v>-1.6500000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>10.96</v>
+        <v>10.97</v>
       </c>
       <c r="F4">
-        <v>10.96</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="G4">
-        <v>12.25</v>
+        <v>12.26</v>
       </c>
       <c r="H4" s="4">
-        <v>457603.51</v>
+        <v>850986.49</v>
       </c>
       <c r="I4">
-        <v>3.98</v>
+        <v>2.98</v>
       </c>
       <c r="J4">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="K4">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="L4">
-        <v>104.79</v>
+        <v>99.67</v>
       </c>
       <c r="M4">
-        <v>4.7</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
@@ -882,37 +894,37 @@
         <v>18</v>
       </c>
       <c r="C5" s="2">
-        <v>48550</v>
+        <v>41600</v>
       </c>
       <c r="D5" s="3">
-        <v>-2.6100000000000002E-2</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E5">
         <v>5.22</v>
       </c>
       <c r="F5">
-        <v>5.22</v>
+        <v>4.24</v>
       </c>
       <c r="G5">
         <v>5.84</v>
       </c>
       <c r="H5" s="4">
-        <v>72566.75</v>
+        <v>82641.210000000006</v>
       </c>
       <c r="I5">
-        <v>4.12</v>
+        <v>4.8099999999999996</v>
       </c>
       <c r="J5">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="K5">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="L5">
-        <v>94.83</v>
+        <v>105.34</v>
       </c>
       <c r="M5">
-        <v>5.2</v>
+        <v>9.0399999999999991</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
@@ -923,37 +935,37 @@
         <v>20</v>
       </c>
       <c r="C6" s="2">
-        <v>75100</v>
+        <v>45150</v>
       </c>
       <c r="D6" s="3">
-        <v>-4.9399999999999999E-2</v>
+        <v>-6.6E-3</v>
       </c>
       <c r="E6">
-        <v>5.69</v>
+        <v>2.89</v>
       </c>
       <c r="F6">
-        <v>5.69</v>
+        <v>4.59</v>
       </c>
       <c r="G6">
-        <v>5.88</v>
+        <v>3.54</v>
       </c>
       <c r="H6" s="4">
-        <v>66692.75</v>
+        <v>55195.19</v>
       </c>
       <c r="I6">
-        <v>3.2</v>
+        <v>2.66</v>
       </c>
       <c r="J6">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="K6">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="L6">
-        <v>100.27</v>
+        <v>106.71</v>
       </c>
       <c r="M6">
-        <v>-2.34</v>
+        <v>8.01</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
@@ -964,37 +976,37 @@
         <v>22</v>
       </c>
       <c r="C7" s="2">
-        <v>69700</v>
+        <v>6280</v>
       </c>
       <c r="D7" s="3">
-        <v>-1.83E-2</v>
+        <v>-4.7999999999999996E-3</v>
       </c>
       <c r="E7">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="F7">
-        <v>2.89</v>
+        <v>5.81</v>
       </c>
       <c r="G7">
-        <v>3.54</v>
+        <v>1.57</v>
       </c>
       <c r="H7" s="4">
-        <v>54191.72</v>
+        <v>10871.34</v>
       </c>
       <c r="I7">
-        <v>1.72</v>
+        <v>3.98</v>
       </c>
       <c r="J7">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="K7">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="L7">
-        <v>100.05</v>
+        <v>94.7</v>
       </c>
       <c r="M7">
-        <v>1.31</v>
+        <v>-7.37</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
@@ -1005,37 +1017,37 @@
         <v>24</v>
       </c>
       <c r="C8" s="2">
-        <v>8610</v>
+        <v>24250</v>
       </c>
       <c r="D8" s="3">
-        <v>-9.1999999999999998E-3</v>
+        <v>-2.0999999999999999E-3</v>
       </c>
       <c r="E8">
-        <v>3.52</v>
+        <v>5.01</v>
       </c>
       <c r="F8">
-        <v>3.52</v>
+        <v>5.73</v>
       </c>
       <c r="G8">
-        <v>5.39</v>
+        <v>5.32</v>
       </c>
       <c r="H8" s="4">
-        <v>21278.16</v>
+        <v>42358.28</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>4.54</v>
       </c>
       <c r="J8">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="K8">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="L8">
-        <v>94.27</v>
+        <v>95.37</v>
       </c>
       <c r="M8">
-        <v>-5.28</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
@@ -1046,37 +1058,37 @@
         <v>26</v>
       </c>
       <c r="C9" s="2">
-        <v>17100</v>
+        <v>508000</v>
       </c>
       <c r="D9" s="3">
-        <v>5.3E-3</v>
+        <v>-2E-3</v>
       </c>
       <c r="E9">
-        <v>1.91</v>
+        <v>36.04</v>
       </c>
       <c r="F9">
-        <v>1.91</v>
+        <v>42.42</v>
       </c>
       <c r="G9">
-        <v>5.53</v>
+        <v>32.08</v>
       </c>
       <c r="H9" s="4">
-        <v>54471.92</v>
+        <v>94588.21</v>
       </c>
       <c r="I9">
-        <v>5.85</v>
+        <v>7.09</v>
       </c>
       <c r="J9">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="K9">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="L9">
-        <v>99.18</v>
+        <v>100.78</v>
       </c>
       <c r="M9">
-        <v>-0.06</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
@@ -1087,37 +1099,37 @@
         <v>28</v>
       </c>
       <c r="C10" s="2">
-        <v>39700</v>
+        <v>26200</v>
       </c>
       <c r="D10" s="3">
-        <v>-5.9200000000000003E-2</v>
+        <v>-9.4999999999999998E-3</v>
       </c>
       <c r="E10">
         <v>5.0599999999999996</v>
       </c>
       <c r="F10">
-        <v>5.0599999999999996</v>
+        <v>10.91</v>
       </c>
       <c r="G10">
         <v>4.7699999999999996</v>
       </c>
       <c r="H10" s="4">
-        <v>45197.48</v>
+        <v>63819.55</v>
       </c>
       <c r="I10">
-        <v>3.02</v>
+        <v>4.58</v>
       </c>
       <c r="J10">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="K10">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="L10">
-        <v>103.66</v>
+        <v>98.34</v>
       </c>
       <c r="M10">
-        <v>4.0599999999999996</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
@@ -1128,37 +1140,37 @@
         <v>30</v>
       </c>
       <c r="C11" s="2">
-        <v>104600</v>
+        <v>112100</v>
       </c>
       <c r="D11" s="3">
-        <v>1.55E-2</v>
+        <v>2.7000000000000001E-3</v>
       </c>
       <c r="E11">
         <v>2.64</v>
       </c>
       <c r="F11">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="G11">
         <v>3.23</v>
       </c>
       <c r="H11" s="4">
-        <v>184176.03</v>
+        <v>201265.59</v>
       </c>
       <c r="I11">
-        <v>2.96</v>
+        <v>2.77</v>
       </c>
       <c r="J11">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="K11">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="L11">
-        <v>111.14</v>
+        <v>97.11</v>
       </c>
       <c r="M11">
-        <v>13.94</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
@@ -1169,37 +1181,37 @@
         <v>32</v>
       </c>
       <c r="C12" s="2">
-        <v>12120</v>
+        <v>14970</v>
       </c>
       <c r="D12" s="3">
-        <v>6.6E-3</v>
+        <v>-1.38E-2</v>
       </c>
       <c r="E12">
         <v>9.0299999999999994</v>
       </c>
       <c r="F12">
-        <v>9.0299999999999994</v>
+        <v>12.44</v>
       </c>
       <c r="G12">
         <v>9.33</v>
       </c>
       <c r="H12" s="4">
-        <v>19594.84</v>
+        <v>22746.58</v>
       </c>
       <c r="I12">
-        <v>4.7</v>
+        <v>3.81</v>
       </c>
       <c r="J12">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="K12">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="L12">
-        <v>99.34</v>
+        <v>101.33</v>
       </c>
       <c r="M12">
-        <v>1.76</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
@@ -1210,37 +1222,37 @@
         <v>34</v>
       </c>
       <c r="C13" s="2">
-        <v>11320</v>
+        <v>84900</v>
       </c>
       <c r="D13" s="3">
-        <v>-1.0500000000000001E-2</v>
+        <v>-1.5100000000000001E-2</v>
       </c>
       <c r="E13">
-        <v>4.49</v>
+        <v>7.58</v>
       </c>
       <c r="F13">
-        <v>4.49</v>
+        <v>11.51</v>
       </c>
       <c r="G13">
-        <v>9.0299999999999994</v>
+        <v>12.29</v>
       </c>
       <c r="H13" s="4">
-        <v>23274.23</v>
+        <v>88767.9</v>
       </c>
       <c r="I13">
-        <v>3.09</v>
+        <v>3.89</v>
       </c>
       <c r="J13">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="K13">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="L13">
-        <v>104.18</v>
+        <v>96.86</v>
       </c>
       <c r="M13">
-        <v>15.63</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
@@ -1251,37 +1263,37 @@
         <v>36</v>
       </c>
       <c r="C14" s="2">
-        <v>572000</v>
+        <v>366500</v>
       </c>
       <c r="D14" s="3">
-        <v>0.04</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="E14">
         <v>8.41</v>
       </c>
       <c r="F14">
-        <v>8.41</v>
+        <v>7.01</v>
       </c>
       <c r="G14">
         <v>11.51</v>
       </c>
       <c r="H14" s="4">
-        <v>436418.31</v>
+        <v>467196.63</v>
       </c>
       <c r="I14">
-        <v>1.75</v>
+        <v>2.73</v>
       </c>
       <c r="J14">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="K14">
-        <v>79</v>
+        <v>34</v>
       </c>
       <c r="L14">
-        <v>110.94</v>
+        <v>92.63</v>
       </c>
       <c r="M14">
-        <v>12.6</v>
+        <v>-11.47</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
@@ -1292,37 +1304,37 @@
         <v>38</v>
       </c>
       <c r="C15" s="2">
-        <v>165000</v>
+        <v>188500</v>
       </c>
       <c r="D15" s="3">
-        <v>1.8499999999999999E-2</v>
+        <v>-2.23E-2</v>
       </c>
       <c r="E15">
-        <v>17.72</v>
+        <v>17.75</v>
       </c>
       <c r="F15">
-        <v>17.72</v>
+        <v>15.91</v>
       </c>
       <c r="G15">
-        <v>17.440000000000001</v>
+        <v>17.45</v>
       </c>
       <c r="H15" s="4">
-        <v>158606.49</v>
+        <v>230365.24</v>
       </c>
       <c r="I15">
-        <v>4.6100000000000003</v>
+        <v>4.03</v>
       </c>
       <c r="J15">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K15">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="L15">
-        <v>98.12</v>
+        <v>100.74</v>
       </c>
       <c r="M15">
-        <v>-1.67</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
@@ -1333,37 +1345,37 @@
         <v>40</v>
       </c>
       <c r="C16" s="2">
-        <v>37700</v>
+        <v>50400</v>
       </c>
       <c r="D16" s="3">
-        <v>-1.95E-2</v>
+        <v>-2E-3</v>
       </c>
       <c r="E16">
-        <v>11.76</v>
+        <v>12.81</v>
       </c>
       <c r="F16">
-        <v>11.76</v>
+        <v>15.02</v>
       </c>
       <c r="G16">
-        <v>9.33</v>
+        <v>16.350000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>25179.95</v>
+        <v>58754.28</v>
       </c>
       <c r="I16">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="J16">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="K16">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="L16">
-        <v>110.01</v>
+        <v>95.84</v>
       </c>
       <c r="M16">
-        <v>11.37</v>
+        <v>-5.79</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
@@ -1374,37 +1386,37 @@
         <v>42</v>
       </c>
       <c r="C17" s="2">
-        <v>51200</v>
+        <v>25550</v>
       </c>
       <c r="D17" s="3">
-        <v>3.4299999999999997E-2</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="E17">
-        <v>15.02</v>
+        <v>11.76</v>
       </c>
       <c r="F17">
-        <v>15.02</v>
+        <v>16.12</v>
       </c>
       <c r="G17">
-        <v>20.7</v>
+        <v>9.33</v>
       </c>
       <c r="H17" s="4">
-        <v>34750.239999999998</v>
+        <v>28036.97</v>
       </c>
       <c r="I17">
-        <v>1.95</v>
+        <v>5.09</v>
       </c>
       <c r="J17">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="K17">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="L17">
-        <v>127.12</v>
+        <v>96.62</v>
       </c>
       <c r="M17">
-        <v>40.85</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
@@ -1415,37 +1427,37 @@
         <v>44</v>
       </c>
       <c r="C18" s="2">
-        <v>211500</v>
+        <v>340000</v>
       </c>
       <c r="D18" s="3">
-        <v>4.19E-2</v>
+        <v>-2.4400000000000002E-2</v>
       </c>
       <c r="E18">
-        <v>12.83</v>
+        <v>17.78</v>
       </c>
       <c r="F18">
-        <v>12.83</v>
+        <v>25.71</v>
       </c>
       <c r="G18">
-        <v>14.29</v>
+        <v>10.4</v>
       </c>
       <c r="H18" s="4">
-        <v>223707.87</v>
+        <v>209715.07</v>
       </c>
       <c r="I18">
-        <v>3.11</v>
+        <v>3.62</v>
       </c>
       <c r="J18">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="K18">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="L18">
-        <v>99.76</v>
+        <v>96.09</v>
       </c>
       <c r="M18">
-        <v>-1.86</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
@@ -1456,37 +1468,37 @@
         <v>46</v>
       </c>
       <c r="C19" s="2">
-        <v>131800</v>
+        <v>85600</v>
       </c>
       <c r="D19" s="3">
-        <v>-5.9200000000000003E-2</v>
+        <v>-4.7000000000000002E-3</v>
       </c>
       <c r="E19">
-        <v>4.74</v>
+        <v>13.09</v>
       </c>
       <c r="F19">
-        <v>4.74</v>
+        <v>18.11</v>
       </c>
       <c r="G19">
-        <v>6.13</v>
+        <v>11.51</v>
       </c>
       <c r="H19" s="4">
-        <v>215808.28</v>
+        <v>96934.29</v>
       </c>
       <c r="I19">
-        <v>1.29</v>
+        <v>4.67</v>
       </c>
       <c r="J19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="K19">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="L19">
-        <v>98.79</v>
+        <v>97.53</v>
       </c>
       <c r="M19">
-        <v>1.46</v>
+        <v>-1.1499999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
@@ -1497,37 +1509,37 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <v>145200</v>
+        <v>5730</v>
       </c>
       <c r="D20" s="3">
-        <v>-2.8799999999999999E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="E20">
-        <v>13.09</v>
+        <v>6.73</v>
       </c>
       <c r="F20">
-        <v>13.09</v>
+        <v>8.8800000000000008</v>
       </c>
       <c r="G20">
-        <v>11.51</v>
+        <v>8.92</v>
       </c>
       <c r="H20" s="4">
-        <v>90347.77</v>
+        <v>22176.36</v>
       </c>
       <c r="I20">
-        <v>2.75</v>
+        <v>5.24</v>
       </c>
       <c r="J20">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>87</v>
+        <v>4</v>
       </c>
       <c r="L20">
-        <v>131.33000000000001</v>
+        <v>102.85</v>
       </c>
       <c r="M20">
-        <v>39.08</v>
+        <v>5.33</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
@@ -1538,37 +1550,37 @@
         <v>50</v>
       </c>
       <c r="C21" s="2">
-        <v>93200</v>
+        <v>89100</v>
       </c>
       <c r="D21" s="3">
-        <v>-2.41E-2</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="E21">
         <v>3.33</v>
       </c>
       <c r="F21">
-        <v>3.33</v>
+        <v>5.48</v>
       </c>
       <c r="G21">
         <v>7.93</v>
       </c>
       <c r="H21" s="4">
-        <v>60299.05</v>
+        <v>72455.820000000007</v>
       </c>
       <c r="I21">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="J21">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="K21">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="L21">
-        <v>100.3</v>
+        <v>94.43</v>
       </c>
       <c r="M21">
-        <v>4.72</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
@@ -1579,37 +1591,37 @@
         <v>52</v>
       </c>
       <c r="C22" s="2">
-        <v>98600</v>
+        <v>73900</v>
       </c>
       <c r="D22" s="3">
-        <v>1.6500000000000001E-2</v>
+        <v>5.4000000000000003E-3</v>
       </c>
       <c r="E22">
-        <v>20.100000000000001</v>
+        <v>20.11</v>
       </c>
       <c r="F22">
-        <v>20.100000000000001</v>
+        <v>32.43</v>
       </c>
       <c r="G22">
-        <v>20.22</v>
+        <v>20.23</v>
       </c>
       <c r="H22" s="4">
-        <v>37882.559999999998</v>
+        <v>30029.13</v>
       </c>
       <c r="I22">
-        <v>14.21</v>
+        <v>18.96</v>
       </c>
       <c r="J22">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="K22">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="L22">
-        <v>103.6</v>
+        <v>99.56</v>
       </c>
       <c r="M22">
-        <v>11.29</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
@@ -1620,37 +1632,37 @@
         <v>54</v>
       </c>
       <c r="C23" s="2">
-        <v>21750</v>
-      </c>
-      <c r="D23" s="3">
-        <v>6.8999999999999999E-3</v>
+        <v>20150</v>
+      </c>
+      <c r="D23" s="5">
+        <v>0</v>
       </c>
       <c r="E23">
         <v>7.7</v>
       </c>
       <c r="F23">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="G23">
         <v>8.18</v>
       </c>
       <c r="H23" s="4">
-        <v>45715.519999999997</v>
+        <v>47065.43</v>
       </c>
       <c r="I23">
-        <v>4.82</v>
+        <v>5.2</v>
       </c>
       <c r="J23">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="K23">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="L23">
-        <v>98.14</v>
+        <v>98.16</v>
       </c>
       <c r="M23">
-        <v>-1.1399999999999999</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
@@ -1661,37 +1673,37 @@
         <v>56</v>
       </c>
       <c r="C24" s="2">
-        <v>51600</v>
-      </c>
-      <c r="D24" s="5">
-        <v>0</v>
+        <v>44000</v>
+      </c>
+      <c r="D24" s="3">
+        <v>-7.9000000000000008E-3</v>
       </c>
       <c r="E24">
         <v>7.45</v>
       </c>
       <c r="F24">
-        <v>7.45</v>
+        <v>7.12</v>
       </c>
       <c r="G24">
         <v>7.69</v>
       </c>
       <c r="H24" s="4">
-        <v>79986.48</v>
+        <v>83445.52</v>
       </c>
       <c r="I24">
-        <v>5.43</v>
+        <v>6.36</v>
       </c>
       <c r="J24">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="K24">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="L24">
-        <v>96.57</v>
+        <v>95.36</v>
       </c>
       <c r="M24">
-        <v>-3.73</v>
+        <v>-4.97</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
@@ -1702,37 +1714,37 @@
         <v>58</v>
       </c>
       <c r="C25" s="2">
-        <v>19180</v>
+        <v>17430</v>
       </c>
       <c r="D25" s="3">
-        <v>3.7000000000000002E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="E25">
         <v>13.7</v>
       </c>
       <c r="F25">
-        <v>13.7</v>
+        <v>14.67</v>
       </c>
       <c r="G25">
         <v>14.6</v>
       </c>
       <c r="H25" s="4">
-        <v>16125.49</v>
+        <v>15915.66</v>
       </c>
       <c r="I25">
-        <v>6.41</v>
+        <v>7.06</v>
       </c>
       <c r="J25">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>98.22</v>
+        <v>92.7</v>
       </c>
       <c r="M25">
-        <v>-1.03</v>
+        <v>-8.7899999999999991</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
@@ -1743,37 +1755,37 @@
         <v>60</v>
       </c>
       <c r="C26" s="2">
-        <v>59500</v>
+        <v>53200</v>
       </c>
       <c r="D26" s="3">
-        <v>1.7100000000000001E-2</v>
+        <v>-3.7000000000000002E-3</v>
       </c>
       <c r="E26">
         <v>10.220000000000001</v>
       </c>
       <c r="F26">
-        <v>10.220000000000001</v>
+        <v>7.26</v>
       </c>
       <c r="G26">
         <v>6.37</v>
       </c>
       <c r="H26" s="4">
-        <v>71885.83</v>
+        <v>77911.67</v>
       </c>
       <c r="I26">
-        <v>4.03</v>
+        <v>4.51</v>
       </c>
       <c r="J26">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="K26">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="L26">
-        <v>96.86</v>
+        <v>99.7</v>
       </c>
       <c r="M26">
-        <v>-2.46</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
@@ -1784,37 +1796,37 @@
         <v>62</v>
       </c>
       <c r="C27" s="2">
-        <v>15370</v>
+        <v>14190</v>
       </c>
       <c r="D27" s="3">
-        <v>-1.9E-3</v>
+        <v>-3.3399999999999999E-2</v>
       </c>
       <c r="E27">
         <v>6.01</v>
       </c>
       <c r="F27">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="G27">
         <v>5.97</v>
       </c>
       <c r="H27" s="4">
-        <v>20769.650000000001</v>
+        <v>21371.81</v>
       </c>
       <c r="I27">
-        <v>4.29</v>
+        <v>4.6500000000000004</v>
       </c>
       <c r="J27">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K27">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="L27">
-        <v>93.48</v>
+        <v>95.56</v>
       </c>
       <c r="M27">
-        <v>-4.71</v>
+        <v>-4.57</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
@@ -1825,37 +1837,37 @@
         <v>64</v>
       </c>
       <c r="C28" s="2">
-        <v>300000</v>
+        <v>172800</v>
       </c>
       <c r="D28" s="3">
-        <v>6.7000000000000002E-3</v>
+        <v>-5.7999999999999996E-3</v>
       </c>
       <c r="E28">
-        <v>4.66</v>
+        <v>11.77</v>
       </c>
       <c r="F28">
-        <v>4.66</v>
+        <v>15.22</v>
       </c>
       <c r="G28">
-        <v>4.88</v>
+        <v>11.4</v>
       </c>
       <c r="H28" s="4">
-        <v>324173.33</v>
+        <v>93205.47</v>
       </c>
       <c r="I28">
-        <v>1.77</v>
+        <v>3.47</v>
       </c>
       <c r="J28">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="K28">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="L28">
-        <v>121.16</v>
+        <v>99.75</v>
       </c>
       <c r="M28">
-        <v>25.79</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
@@ -1866,37 +1878,37 @@
         <v>66</v>
       </c>
       <c r="C29" s="2">
-        <v>176700</v>
+        <v>14420</v>
       </c>
       <c r="D29" s="3">
-        <v>7.4000000000000003E-3</v>
+        <v>-1.37E-2</v>
       </c>
       <c r="E29">
-        <v>11.77</v>
+        <v>8.11</v>
       </c>
       <c r="F29">
-        <v>11.77</v>
+        <v>8.59</v>
       </c>
       <c r="G29">
-        <v>11.4</v>
+        <v>9.93</v>
       </c>
       <c r="H29" s="4">
-        <v>85735.74</v>
+        <v>19725.37</v>
       </c>
       <c r="I29">
-        <v>3.4</v>
+        <v>6.59</v>
       </c>
       <c r="J29">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>95</v>
+        <v>7</v>
       </c>
       <c r="L29">
-        <v>104.67</v>
+        <v>98.68</v>
       </c>
       <c r="M29">
-        <v>11.48</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
@@ -1907,37 +1919,37 @@
         <v>68</v>
       </c>
       <c r="C30" s="2">
-        <v>16300</v>
+        <v>35650</v>
       </c>
       <c r="D30" s="3">
-        <v>-6.7000000000000002E-3</v>
+        <v>-2.06E-2</v>
       </c>
       <c r="E30">
-        <v>8.11</v>
+        <v>1.23</v>
       </c>
       <c r="F30">
-        <v>8.11</v>
+        <v>4.99</v>
       </c>
       <c r="G30">
-        <v>9.93</v>
+        <v>1.59</v>
       </c>
       <c r="H30" s="4">
-        <v>19583.27</v>
+        <v>134749.68</v>
       </c>
       <c r="I30">
-        <v>5.83</v>
+        <v>3.24</v>
       </c>
       <c r="J30">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="K30">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L30">
-        <v>96.55</v>
+        <v>97.72</v>
       </c>
       <c r="M30">
-        <v>-2.63</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
@@ -1948,37 +1960,37 @@
         <v>70</v>
       </c>
       <c r="C31" s="2">
-        <v>38450</v>
+        <v>261500</v>
       </c>
       <c r="D31" s="3">
-        <v>1.5900000000000001E-2</v>
+        <v>-5.7000000000000002E-3</v>
       </c>
       <c r="E31">
-        <v>1.23</v>
+        <v>18.12</v>
       </c>
       <c r="F31">
-        <v>1.23</v>
+        <v>25.42</v>
       </c>
       <c r="G31">
-        <v>1.59</v>
+        <v>14.46</v>
       </c>
       <c r="H31" s="4">
-        <v>118301.94</v>
+        <v>288207.19</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="J31">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K31">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="L31">
-        <v>104.24</v>
+        <v>95.4</v>
       </c>
       <c r="M31">
-        <v>6.36</v>
+        <v>-2.2400000000000002</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
@@ -1989,37 +2001,37 @@
         <v>72</v>
       </c>
       <c r="C32" s="2">
-        <v>98900</v>
+        <v>57100</v>
       </c>
       <c r="D32" s="3">
-        <v>1.6400000000000001E-2</v>
+        <v>-1.21E-2</v>
       </c>
       <c r="E32">
-        <v>8.7200000000000006</v>
+        <v>9.27</v>
       </c>
       <c r="F32">
-        <v>8.7200000000000006</v>
+        <v>12.34</v>
       </c>
       <c r="G32">
-        <v>8.4</v>
+        <v>10.26</v>
       </c>
       <c r="H32" s="4">
-        <v>120617.68</v>
+        <v>41033.660000000003</v>
       </c>
       <c r="I32">
-        <v>2.62</v>
+        <v>3.24</v>
       </c>
       <c r="J32">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="K32">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="L32">
-        <v>101.29</v>
+        <v>105.05</v>
       </c>
       <c r="M32">
-        <v>2.2799999999999998</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
@@ -2030,37 +2042,37 @@
         <v>74</v>
       </c>
       <c r="C33" s="2">
-        <v>276000</v>
+        <v>37900</v>
       </c>
       <c r="D33" s="3">
-        <v>-5.3199999999999997E-2</v>
+        <v>1.0699999999999999E-2</v>
       </c>
       <c r="E33">
-        <v>18.66</v>
+        <v>32.619999999999997</v>
       </c>
       <c r="F33">
-        <v>18.66</v>
+        <v>34.020000000000003</v>
       </c>
       <c r="G33">
-        <v>13</v>
+        <v>22.33</v>
       </c>
       <c r="H33" s="4">
-        <v>195836.08</v>
+        <v>19757</v>
       </c>
       <c r="I33">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="K33">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="L33">
-        <v>111.31</v>
+        <v>99.42</v>
       </c>
       <c r="M33">
-        <v>15.48</v>
+        <v>-3.81</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
@@ -2071,37 +2083,37 @@
         <v>76</v>
       </c>
       <c r="C34" s="2">
-        <v>78600</v>
+        <v>111100</v>
       </c>
       <c r="D34" s="3">
-        <v>2.2100000000000002E-2</v>
+        <v>-1.9400000000000001E-2</v>
       </c>
       <c r="E34">
-        <v>5.55</v>
+        <v>8.7200000000000006</v>
       </c>
       <c r="F34">
-        <v>5.55</v>
+        <v>9.17</v>
       </c>
       <c r="G34">
-        <v>6.57</v>
+        <v>8.4</v>
       </c>
       <c r="H34" s="4">
-        <v>155269.29999999999</v>
+        <v>128023.67999999999</v>
       </c>
       <c r="I34">
-        <v>3.82</v>
+        <v>2.33</v>
       </c>
       <c r="J34">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="K34">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="L34">
-        <v>108.26</v>
+        <v>101.34</v>
       </c>
       <c r="M34">
-        <v>14.58</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
@@ -2112,37 +2124,37 @@
         <v>78</v>
       </c>
       <c r="C35" s="2">
-        <v>128800</v>
+        <v>16210</v>
       </c>
       <c r="D35" s="3">
-        <v>2.63E-2</v>
+        <v>-1.7600000000000001E-2</v>
       </c>
       <c r="E35">
-        <v>9.17</v>
+        <v>6.77</v>
       </c>
       <c r="F35">
-        <v>9.17</v>
+        <v>7.15</v>
       </c>
       <c r="G35">
-        <v>9.1</v>
+        <v>10.97</v>
       </c>
       <c r="H35" s="4">
-        <v>162088.94</v>
+        <v>24488.799999999999</v>
       </c>
       <c r="I35">
-        <v>3.19</v>
+        <v>6.17</v>
       </c>
       <c r="J35">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="K35">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="L35">
-        <v>106.82</v>
+        <v>99.6</v>
       </c>
       <c r="M35">
-        <v>9.99</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.4">
@@ -2153,37 +2165,37 @@
         <v>80</v>
       </c>
       <c r="C36" s="2">
-        <v>161200</v>
+        <v>183000</v>
       </c>
       <c r="D36" s="3">
-        <v>1.4500000000000001E-2</v>
+        <v>-1.4E-2</v>
       </c>
       <c r="E36">
-        <v>9.98</v>
+        <v>18.66</v>
       </c>
       <c r="F36">
-        <v>9.98</v>
+        <v>24.44</v>
       </c>
       <c r="G36">
-        <v>9.08</v>
+        <v>13</v>
       </c>
       <c r="H36" s="4">
-        <v>159779.29999999999</v>
+        <v>234850.32</v>
       </c>
       <c r="I36">
-        <v>2.71</v>
+        <v>4.75</v>
       </c>
       <c r="J36">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="K36">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="L36">
-        <v>103.12</v>
+        <v>96.42</v>
       </c>
       <c r="M36">
-        <v>3.33</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.4">
@@ -2194,37 +2206,37 @@
         <v>82</v>
       </c>
       <c r="C37" s="2">
-        <v>18200</v>
-      </c>
-      <c r="D37" s="3">
-        <v>3.8999999999999998E-3</v>
+        <v>114000</v>
+      </c>
+      <c r="D37" s="5">
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>7.58</v>
+        <v>5.55</v>
       </c>
       <c r="F37">
-        <v>7.58</v>
+        <v>15.37</v>
       </c>
       <c r="G37">
-        <v>6.97</v>
+        <v>6.57</v>
       </c>
       <c r="H37" s="4">
-        <v>34779.699999999997</v>
+        <v>173176.01</v>
       </c>
       <c r="I37">
-        <v>4.04</v>
+        <v>2.63</v>
       </c>
       <c r="J37">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K37">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="L37">
-        <v>98.81</v>
+        <v>95.16</v>
       </c>
       <c r="M37">
-        <v>3.06</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.4">
@@ -2235,37 +2247,37 @@
         <v>84</v>
       </c>
       <c r="C38" s="2">
-        <v>19250</v>
+        <v>133700</v>
       </c>
       <c r="D38" s="3">
-        <v>1.4200000000000001E-2</v>
+        <v>-2.76E-2</v>
       </c>
       <c r="E38">
-        <v>7.27</v>
+        <v>9.17</v>
       </c>
       <c r="F38">
-        <v>7.27</v>
+        <v>9.11</v>
       </c>
       <c r="G38">
-        <v>5.87</v>
+        <v>9.1</v>
       </c>
       <c r="H38" s="4">
-        <v>38724.660000000003</v>
+        <v>175497.01</v>
       </c>
       <c r="I38">
-        <v>3.64</v>
+        <v>3.07</v>
       </c>
       <c r="J38">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="K38">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L38">
-        <v>105.27</v>
+        <v>99.53</v>
       </c>
       <c r="M38">
-        <v>12.84</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.4">
@@ -2276,37 +2288,37 @@
         <v>86</v>
       </c>
       <c r="C39" s="2">
-        <v>64700</v>
+        <v>175700</v>
       </c>
       <c r="D39" s="3">
-        <v>8.7400000000000005E-2</v>
+        <v>-1.95E-2</v>
       </c>
       <c r="E39">
-        <v>9.39</v>
+        <v>9.98</v>
       </c>
       <c r="F39">
-        <v>9.39</v>
+        <v>10.47</v>
       </c>
       <c r="G39">
-        <v>9.34</v>
+        <v>9.08</v>
       </c>
       <c r="H39" s="4">
-        <v>98085.37</v>
+        <v>172315.78</v>
       </c>
       <c r="I39">
-        <v>3.55</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="J39">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="K39">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="L39">
-        <v>107.51</v>
+        <v>102.39</v>
       </c>
       <c r="M39">
-        <v>5.2</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.4">
@@ -2317,37 +2329,37 @@
         <v>88</v>
       </c>
       <c r="C40" s="2">
-        <v>26350</v>
+        <v>15750</v>
       </c>
       <c r="D40" s="3">
-        <v>-7.4999999999999997E-3</v>
+        <v>1.9E-3</v>
       </c>
       <c r="E40">
-        <v>12.36</v>
+        <v>7.58</v>
       </c>
       <c r="F40">
-        <v>12.36</v>
+        <v>6.98</v>
       </c>
       <c r="G40">
-        <v>12.46</v>
+        <v>6.97</v>
       </c>
       <c r="H40" s="4">
-        <v>31515.31</v>
+        <v>35520.300000000003</v>
       </c>
       <c r="I40">
-        <v>4.33</v>
+        <v>4.67</v>
       </c>
       <c r="J40">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="K40">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L40">
-        <v>89.68</v>
+        <v>102.91</v>
       </c>
       <c r="M40">
-        <v>-13.75</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.4">
@@ -2358,37 +2370,37 @@
         <v>90</v>
       </c>
       <c r="C41" s="2">
-        <v>11550</v>
+        <v>18190</v>
       </c>
       <c r="D41" s="3">
-        <v>1.8499999999999999E-2</v>
+        <v>-4.8999999999999998E-3</v>
       </c>
       <c r="E41">
-        <v>1.55</v>
+        <v>7.27</v>
       </c>
       <c r="F41">
-        <v>1.55</v>
+        <v>6.91</v>
       </c>
       <c r="G41">
-        <v>6.05</v>
+        <v>5.87</v>
       </c>
       <c r="H41" s="4">
-        <v>29736.69</v>
+        <v>40231.230000000003</v>
       </c>
       <c r="I41">
-        <v>2.16</v>
+        <v>3.85</v>
       </c>
       <c r="J41">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="K41">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="L41">
-        <v>101.21</v>
+        <v>100.56</v>
       </c>
       <c r="M41">
-        <v>2.48</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.4">
@@ -2399,37 +2411,37 @@
         <v>92</v>
       </c>
       <c r="C42" s="2">
-        <v>59000</v>
+        <v>31050</v>
       </c>
       <c r="D42" s="3">
-        <v>1.6999999999999999E-3</v>
+        <v>-1.5800000000000002E-2</v>
       </c>
       <c r="E42">
-        <v>11.33</v>
+        <v>12.36</v>
       </c>
       <c r="F42">
-        <v>11.33</v>
+        <v>12.37</v>
       </c>
       <c r="G42">
-        <v>16.21</v>
+        <v>12.46</v>
       </c>
       <c r="H42" s="4">
-        <v>59573.64</v>
+        <v>32701.97</v>
       </c>
       <c r="I42">
-        <v>2.0299999999999998</v>
+        <v>3.67</v>
       </c>
       <c r="J42">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="K42">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="L42">
-        <v>110.64</v>
+        <v>104.3</v>
       </c>
       <c r="M42">
-        <v>20.65</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.4">
@@ -2440,37 +2452,37 @@
         <v>94</v>
       </c>
       <c r="C43" s="2">
-        <v>19650</v>
+        <v>18090</v>
       </c>
       <c r="D43" s="3">
-        <v>1.7600000000000001E-2</v>
+        <v>-1.6999999999999999E-3</v>
       </c>
       <c r="E43">
         <v>8.8800000000000008</v>
       </c>
       <c r="F43">
-        <v>8.8800000000000008</v>
+        <v>12.05</v>
       </c>
       <c r="G43">
         <v>10.31</v>
       </c>
       <c r="H43" s="4">
-        <v>26617.85</v>
+        <v>28552.560000000001</v>
       </c>
       <c r="I43">
-        <v>5.98</v>
+        <v>6.5</v>
       </c>
       <c r="J43">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K43">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L43">
-        <v>105</v>
+        <v>96.58</v>
       </c>
       <c r="M43">
-        <v>10.02</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.4">
@@ -2481,37 +2493,119 @@
         <v>96</v>
       </c>
       <c r="C44" s="2">
-        <v>33200</v>
+        <v>59400</v>
       </c>
       <c r="D44" s="3">
-        <v>1.84E-2</v>
+        <v>-1.8200000000000001E-2</v>
       </c>
       <c r="E44">
+        <v>5.71</v>
+      </c>
+      <c r="F44">
+        <v>6.85</v>
+      </c>
+      <c r="G44">
+        <v>10.42</v>
+      </c>
+      <c r="H44" s="4">
+        <v>82108.259999999995</v>
+      </c>
+      <c r="I44">
+        <v>2.86</v>
+      </c>
+      <c r="J44">
+        <v>61</v>
+      </c>
+      <c r="K44">
+        <v>61</v>
+      </c>
+      <c r="L44">
+        <v>96.23</v>
+      </c>
+      <c r="M44">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A45" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B45" t="s">
+        <v>98</v>
+      </c>
+      <c r="C45" s="2">
+        <v>36150</v>
+      </c>
+      <c r="D45" s="3">
+        <v>-4.1000000000000003E-3</v>
+      </c>
+      <c r="E45">
         <v>8.91</v>
       </c>
-      <c r="F44">
-        <v>8.91</v>
-      </c>
-      <c r="G44">
+      <c r="F45">
+        <v>8.7100000000000009</v>
+      </c>
+      <c r="G45">
         <v>8.8699999999999992</v>
       </c>
-      <c r="H44" s="4">
-        <v>49113.23</v>
-      </c>
-      <c r="I44">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="J44">
-        <v>73</v>
-      </c>
-      <c r="K44">
-        <v>73</v>
-      </c>
-      <c r="L44">
-        <v>98.02</v>
-      </c>
-      <c r="M44">
-        <v>-0.6</v>
+      <c r="H45" s="4">
+        <v>53410.39</v>
+      </c>
+      <c r="I45">
+        <v>3.76</v>
+      </c>
+      <c r="J45">
+        <v>83</v>
+      </c>
+      <c r="K45">
+        <v>83</v>
+      </c>
+      <c r="L45">
+        <v>106.06</v>
+      </c>
+      <c r="M45">
+        <v>13.15</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A46" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C46" s="2">
+        <v>8020</v>
+      </c>
+      <c r="D46" s="3">
+        <v>-5.0000000000000001E-3</v>
+      </c>
+      <c r="E46">
+        <v>7.01</v>
+      </c>
+      <c r="F46">
+        <v>5.7</v>
+      </c>
+      <c r="G46">
+        <v>6.97</v>
+      </c>
+      <c r="H46" s="4">
+        <v>27249.11</v>
+      </c>
+      <c r="I46">
+        <v>3.62</v>
+      </c>
+      <c r="J46">
+        <v>41</v>
+      </c>
+      <c r="K46">
+        <v>41</v>
+      </c>
+      <c r="L46">
+        <v>98.68</v>
+      </c>
+      <c r="M46">
+        <v>-1.6</v>
       </c>
     </row>
   </sheetData>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD69560F-9D1A-4D0C-8E0D-03DBE72B4D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2B2C6BB-5DB1-42EF-828E-EE18C5415F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{7DCE6202-A540-4832-9A21-B34225140D9C}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8F1BA191-F7EC-4856-81FF-AD9496DA4ADC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -705,7 +705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B55D34-54E5-4ED8-828A-0F25C2BD0D6C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E38A2DA-1B90-4D3C-A15D-92F411405AA2}">
   <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
@@ -798,7 +798,7 @@
         <v>55</v>
       </c>
       <c r="L2">
-        <v>101.28</v>
+        <v>97.94</v>
       </c>
       <c r="M2">
         <v>3.56</v>
@@ -839,7 +839,7 @@
         <v>41</v>
       </c>
       <c r="L3">
-        <v>94.7</v>
+        <v>80.510000000000005</v>
       </c>
       <c r="M3">
         <v>-7.53</v>
@@ -880,7 +880,7 @@
         <v>82</v>
       </c>
       <c r="L4">
-        <v>99.67</v>
+        <v>112.43</v>
       </c>
       <c r="M4">
         <v>2.99</v>
@@ -921,7 +921,7 @@
         <v>55</v>
       </c>
       <c r="L5">
-        <v>105.34</v>
+        <v>98.19</v>
       </c>
       <c r="M5">
         <v>9.0399999999999991</v>
@@ -962,7 +962,7 @@
         <v>40</v>
       </c>
       <c r="L6">
-        <v>106.71</v>
+        <v>85.62</v>
       </c>
       <c r="M6">
         <v>8.01</v>
@@ -1003,7 +1003,7 @@
         <v>21</v>
       </c>
       <c r="L7">
-        <v>94.7</v>
+        <v>84.57</v>
       </c>
       <c r="M7">
         <v>-7.37</v>
@@ -1044,7 +1044,7 @@
         <v>66</v>
       </c>
       <c r="L8">
-        <v>95.37</v>
+        <v>96.05</v>
       </c>
       <c r="M8">
         <v>-5.46</v>
@@ -1126,7 +1126,7 @@
         <v>36</v>
       </c>
       <c r="L10">
-        <v>98.34</v>
+        <v>81.430000000000007</v>
       </c>
       <c r="M10">
         <v>0.96</v>
@@ -1167,7 +1167,7 @@
         <v>42</v>
       </c>
       <c r="L11">
-        <v>97.11</v>
+        <v>105.74</v>
       </c>
       <c r="M11">
         <v>-1.23</v>
@@ -1208,7 +1208,7 @@
         <v>94</v>
       </c>
       <c r="L12">
-        <v>101.33</v>
+        <v>110.94</v>
       </c>
       <c r="M12">
         <v>4.0999999999999996</v>
@@ -1249,7 +1249,7 @@
         <v>59</v>
       </c>
       <c r="L13">
-        <v>96.86</v>
+        <v>113.45</v>
       </c>
       <c r="M13">
         <v>-3.52</v>
@@ -1290,7 +1290,7 @@
         <v>34</v>
       </c>
       <c r="L14">
-        <v>92.63</v>
+        <v>71.63</v>
       </c>
       <c r="M14">
         <v>-11.47</v>
@@ -1331,7 +1331,7 @@
         <v>84</v>
       </c>
       <c r="L15">
-        <v>100.74</v>
+        <v>112.57</v>
       </c>
       <c r="M15">
         <v>4.43</v>
@@ -1372,7 +1372,7 @@
         <v>49</v>
       </c>
       <c r="L16">
-        <v>95.84</v>
+        <v>82.68</v>
       </c>
       <c r="M16">
         <v>-5.79</v>
@@ -1413,7 +1413,7 @@
         <v>50</v>
       </c>
       <c r="L17">
-        <v>96.62</v>
+        <v>82.24</v>
       </c>
       <c r="M17">
         <v>-1.54</v>
@@ -1454,7 +1454,7 @@
         <v>64</v>
       </c>
       <c r="L18">
-        <v>96.09</v>
+        <v>86.65</v>
       </c>
       <c r="M18">
         <v>-3.82</v>
@@ -1495,7 +1495,7 @@
         <v>42</v>
       </c>
       <c r="L19">
-        <v>97.53</v>
+        <v>81.13</v>
       </c>
       <c r="M19">
         <v>-1.1499999999999999</v>
@@ -1536,7 +1536,7 @@
         <v>4</v>
       </c>
       <c r="L20">
-        <v>102.85</v>
+        <v>98.87</v>
       </c>
       <c r="M20">
         <v>5.33</v>
@@ -1577,7 +1577,7 @@
         <v>48</v>
       </c>
       <c r="L21">
-        <v>94.43</v>
+        <v>96.9</v>
       </c>
       <c r="M21">
         <v>-12.9</v>
@@ -1618,7 +1618,7 @@
         <v>57</v>
       </c>
       <c r="L22">
-        <v>99.56</v>
+        <v>90.64</v>
       </c>
       <c r="M22">
         <v>0.54</v>
@@ -1659,7 +1659,7 @@
         <v>55</v>
       </c>
       <c r="L23">
-        <v>98.16</v>
+        <v>93.19</v>
       </c>
       <c r="M23">
         <v>-0.25</v>
@@ -1700,7 +1700,7 @@
         <v>39</v>
       </c>
       <c r="L24">
-        <v>95.36</v>
+        <v>86.82</v>
       </c>
       <c r="M24">
         <v>-4.97</v>
@@ -1741,7 +1741,7 @@
         <v>10</v>
       </c>
       <c r="L25">
-        <v>92.7</v>
+        <v>90.07</v>
       </c>
       <c r="M25">
         <v>-8.7899999999999991</v>
@@ -1782,7 +1782,7 @@
         <v>60</v>
       </c>
       <c r="L26">
-        <v>99.7</v>
+        <v>94.27</v>
       </c>
       <c r="M26">
         <v>1.33</v>
@@ -1823,7 +1823,7 @@
         <v>50</v>
       </c>
       <c r="L27">
-        <v>95.56</v>
+        <v>92.21</v>
       </c>
       <c r="M27">
         <v>-4.57</v>
@@ -1864,7 +1864,7 @@
         <v>83</v>
       </c>
       <c r="L28">
-        <v>99.75</v>
+        <v>99.67</v>
       </c>
       <c r="M28">
         <v>-0.23</v>
@@ -1905,7 +1905,7 @@
         <v>7</v>
       </c>
       <c r="L29">
-        <v>98.68</v>
+        <v>91</v>
       </c>
       <c r="M29">
         <v>-0.48</v>
@@ -1946,7 +1946,7 @@
         <v>31</v>
       </c>
       <c r="L30">
-        <v>97.72</v>
+        <v>99.12</v>
       </c>
       <c r="M30">
         <v>-2.33</v>
@@ -1987,7 +1987,7 @@
         <v>43</v>
       </c>
       <c r="L31">
-        <v>95.4</v>
+        <v>71.8</v>
       </c>
       <c r="M31">
         <v>-2.2400000000000002</v>
@@ -2028,7 +2028,7 @@
         <v>50</v>
       </c>
       <c r="L32">
-        <v>105.05</v>
+        <v>89.25</v>
       </c>
       <c r="M32">
         <v>6.53</v>
@@ -2069,7 +2069,7 @@
         <v>35</v>
       </c>
       <c r="L33">
-        <v>99.42</v>
+        <v>74.89</v>
       </c>
       <c r="M33">
         <v>-3.81</v>
@@ -2110,7 +2110,7 @@
         <v>94</v>
       </c>
       <c r="L34">
-        <v>101.34</v>
+        <v>109.62</v>
       </c>
       <c r="M34">
         <v>7.55</v>
@@ -2151,7 +2151,7 @@
         <v>13</v>
       </c>
       <c r="L35">
-        <v>99.6</v>
+        <v>95.79</v>
       </c>
       <c r="M35">
         <v>1.44</v>
@@ -2192,7 +2192,7 @@
         <v>54</v>
       </c>
       <c r="L36">
-        <v>96.42</v>
+        <v>81.08</v>
       </c>
       <c r="M36">
         <v>-0.16</v>
@@ -2233,7 +2233,7 @@
         <v>81</v>
       </c>
       <c r="L37">
-        <v>95.16</v>
+        <v>135.54</v>
       </c>
       <c r="M37">
         <v>-0.52</v>
@@ -2274,7 +2274,7 @@
         <v>92</v>
       </c>
       <c r="L38">
-        <v>99.53</v>
+        <v>107.94</v>
       </c>
       <c r="M38">
         <v>3.89</v>
@@ -2315,7 +2315,7 @@
         <v>88</v>
       </c>
       <c r="L39">
-        <v>102.39</v>
+        <v>107.65</v>
       </c>
       <c r="M39">
         <v>7.73</v>
@@ -2356,7 +2356,7 @@
         <v>57</v>
       </c>
       <c r="L40">
-        <v>102.91</v>
+        <v>90.85</v>
       </c>
       <c r="M40">
         <v>9.68</v>
@@ -2397,7 +2397,7 @@
         <v>75</v>
       </c>
       <c r="L41">
-        <v>100.56</v>
+        <v>102.02</v>
       </c>
       <c r="M41">
         <v>6.31</v>
@@ -2438,7 +2438,7 @@
         <v>76</v>
       </c>
       <c r="L42">
-        <v>104.3</v>
+        <v>110.69</v>
       </c>
       <c r="M42">
         <v>13.94</v>
@@ -2479,7 +2479,7 @@
         <v>12</v>
       </c>
       <c r="L43">
-        <v>96.58</v>
+        <v>94.1</v>
       </c>
       <c r="M43">
         <v>-4.29</v>
@@ -2520,7 +2520,7 @@
         <v>61</v>
       </c>
       <c r="L44">
-        <v>96.23</v>
+        <v>91.89</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -2561,7 +2561,7 @@
         <v>83</v>
       </c>
       <c r="L45">
-        <v>106.06</v>
+        <v>110.35</v>
       </c>
       <c r="M45">
         <v>13.15</v>
@@ -2602,7 +2602,7 @@
         <v>41</v>
       </c>
       <c r="L46">
-        <v>98.68</v>
+        <v>96.6</v>
       </c>
       <c r="M46">
         <v>-1.6</v>

--- a/1.xlsx
+++ b/1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F2B2C6BB-5DB1-42EF-828E-EE18C5415F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7172CCC-26C3-4C1E-9AB8-FA1E2E4622EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{8F1BA191-F7EC-4856-81FF-AD9496DA4ADC}"/>
   </bookViews>
